--- a/ig/main/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2318" uniqueCount="2315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="2341">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-31T12:00:00+01:00</t>
+    <t>2025-03-28T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -663,7 +663,7 @@
     <t>0169</t>
   </si>
   <si>
-    <t>Détection du dopage</t>
+    <t>Dépistage et prise en charge du dopage</t>
   </si>
   <si>
     <t>0172</t>
@@ -1035,7 +1035,7 @@
     <t>0266</t>
   </si>
   <si>
-    <t>Interruption thérapeutique de grossesse</t>
+    <t>Interruption de grossesse pour motif médical (IMG/ITG)</t>
   </si>
   <si>
     <t>0267</t>
@@ -2733,7 +2733,7 @@
     <t>0723</t>
   </si>
   <si>
-    <t>Accompagnement à la réinsertion professionnelle</t>
+    <t>Accompagnement à l'insertion ou la réinsertion professionnelle</t>
   </si>
   <si>
     <t>0724</t>
@@ -4923,7 +4923,7 @@
     <t>1140</t>
   </si>
   <si>
-    <t>Bilan radiologique chez les patients différents (handicaps physiques, psychiques, claustrophobie, …)</t>
+    <t>Bilan radiologique avec prise en charge adaptée (handicaps physiques, psychiques, claustrophobie, …)</t>
   </si>
   <si>
     <t>1141</t>
@@ -6774,12 +6774,6 @@
     <t>Délivrance de certificats spécifiques pour les sportifs en situation de Handicap</t>
   </si>
   <si>
-    <t>1466</t>
-  </si>
-  <si>
-    <t>Dépistage et prise en charge du dopage</t>
-  </si>
-  <si>
     <t>1467</t>
   </si>
   <si>
@@ -6834,12 +6828,6 @@
     <t>Analyse tridimensionnelle du mouvement, de la marche</t>
   </si>
   <si>
-    <t>1476</t>
-  </si>
-  <si>
-    <t>Accès direct Infirmier en Pratique Avancée (IPA), kinésithérapeute, orthophoniste</t>
-  </si>
-  <si>
     <t>1477</t>
   </si>
   <si>
@@ -6952,6 +6940,96 @@
   </si>
   <si>
     <t>HandiBloc</t>
+  </si>
+  <si>
+    <t>1496</t>
+  </si>
+  <si>
+    <t>Accompagnement des troubles de l'écriture</t>
+  </si>
+  <si>
+    <t>1497</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique à l'accès aux nouvelles technologies</t>
+  </si>
+  <si>
+    <t>1498</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique auprès des proches aidants (proches et professionnels) : apprentissage de techniques d'accompagnement</t>
+  </si>
+  <si>
+    <t>1499</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de déficiences visuelles</t>
+  </si>
+  <si>
+    <t>1500</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de maladies neuro-évolutives (SLA, SEP, Parkinson, Alzheimer, PNM)</t>
+  </si>
+  <si>
+    <t>1501</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de particularités sensorielles (TND)</t>
+  </si>
+  <si>
+    <t>1502</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique dans le cadre de pathologies neurologiques (AVC, TCE)</t>
+  </si>
+  <si>
+    <t>1503</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique de rééducation/réadaptation en situation de vie quotidienne post-hospitalisation (RAD)</t>
+  </si>
+  <si>
+    <t>1504</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique des troubles alimentaires</t>
+  </si>
+  <si>
+    <t>1505</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique pour la prévention de la chute et ses conséquences : désadaptation psychomotrice</t>
+  </si>
+  <si>
+    <t>1506</t>
+  </si>
+  <si>
+    <t>Evaluation et accompagnement à la mise en place de communication augmentative-alternative</t>
+  </si>
+  <si>
+    <t>1507</t>
+  </si>
+  <si>
+    <t>Programme de prévention primaire ergothérapique « Bien vieillir » (TaPasS)</t>
+  </si>
+  <si>
+    <t>1508</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique en milieu scolaire</t>
+  </si>
+  <si>
+    <t>1509</t>
+  </si>
+  <si>
+    <t>Accompagnement ergothérapique en réhabilitation psycho-sociale</t>
+  </si>
+  <si>
+    <t>1510</t>
+  </si>
+  <si>
+    <t>Evaluation et accompagnement ergothérapique au positionnement au fauteuil roulant (MCPAA) et positionnement au lit</t>
   </si>
   <si>
     <t>System URI</t>
@@ -7225,7 +7303,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1145"/>
+  <dimension ref="A1:B1158"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16378,18 +16456,122 @@
     </row>
     <row r="1144">
       <c r="A1144" t="s" s="2">
-        <v>21</v>
+        <v>2313</v>
       </c>
       <c r="B1144" t="s" s="2">
-        <v>21</v>
+        <v>2314</v>
       </c>
     </row>
     <row r="1145">
       <c r="A1145" t="s" s="2">
-        <v>2313</v>
+        <v>2315</v>
       </c>
       <c r="B1145" t="s" s="2">
-        <v>2314</v>
+        <v>2316</v>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="s" s="2">
+        <v>2317</v>
+      </c>
+      <c r="B1146" t="s" s="2">
+        <v>2318</v>
+      </c>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="s" s="2">
+        <v>2319</v>
+      </c>
+      <c r="B1147" t="s" s="2">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="s" s="2">
+        <v>2321</v>
+      </c>
+      <c r="B1148" t="s" s="2">
+        <v>2322</v>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="s" s="2">
+        <v>2323</v>
+      </c>
+      <c r="B1149" t="s" s="2">
+        <v>2324</v>
+      </c>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="s" s="2">
+        <v>2325</v>
+      </c>
+      <c r="B1150" t="s" s="2">
+        <v>2326</v>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="s" s="2">
+        <v>2327</v>
+      </c>
+      <c r="B1151" t="s" s="2">
+        <v>2328</v>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="s" s="2">
+        <v>2329</v>
+      </c>
+      <c r="B1152" t="s" s="2">
+        <v>2330</v>
+      </c>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="s" s="2">
+        <v>2331</v>
+      </c>
+      <c r="B1153" t="s" s="2">
+        <v>2332</v>
+      </c>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="s" s="2">
+        <v>2333</v>
+      </c>
+      <c r="B1154" t="s" s="2">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="s" s="2">
+        <v>2335</v>
+      </c>
+      <c r="B1155" t="s" s="2">
+        <v>2336</v>
+      </c>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="s" s="2">
+        <v>2337</v>
+      </c>
+      <c r="B1156" t="s" s="2">
+        <v>2338</v>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="B1157" t="s" s="2">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="s" s="2">
+        <v>2339</v>
+      </c>
+      <c r="B1158" t="s" s="2">
+        <v>2340</v>
       </c>
     </row>
   </sheetData>

--- a/ig/main/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
+++ b/ig/main/ValueSet-JDV-J16-ActeSpecifique-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2344" uniqueCount="2341">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2346" uniqueCount="2343">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-28T12:00:00+01:00</t>
+    <t>2025-04-25T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -7030,6 +7030,12 @@
   </si>
   <si>
     <t>Evaluation et accompagnement ergothérapique au positionnement au fauteuil roulant (MCPAA) et positionnement au lit</t>
+  </si>
+  <si>
+    <t>1511</t>
+  </si>
+  <si>
+    <t>Accompagnement précoce des déficiences</t>
   </si>
   <si>
     <t>System URI</t>
@@ -7303,7 +7309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B1158"/>
+  <dimension ref="A1:B1159"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -16560,18 +16566,26 @@
     </row>
     <row r="1157">
       <c r="A1157" t="s" s="2">
-        <v>21</v>
+        <v>2339</v>
       </c>
       <c r="B1157" t="s" s="2">
-        <v>21</v>
+        <v>2340</v>
       </c>
     </row>
     <row r="1158">
       <c r="A1158" t="s" s="2">
-        <v>2339</v>
+        <v>21</v>
       </c>
       <c r="B1158" t="s" s="2">
-        <v>2340</v>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="s" s="2">
+        <v>2341</v>
+      </c>
+      <c r="B1159" t="s" s="2">
+        <v>2342</v>
       </c>
     </row>
   </sheetData>
